--- a/data/editable_files/nodes_text.xlsx
+++ b/data/editable_files/nodes_text.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\editable_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5B0895-90E6-4C67-9197-AE6E9179111B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43344817-CB0A-4E26-ABCB-F7BC117978A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32570" yWindow="-11510" windowWidth="23260" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -278,18 +278,6 @@
     <t>Case C1 based on question Q 17</t>
   </si>
   <si>
-    <t>Summarizes the importance of the variables defining individual features to different fishers. The algorithm wmax gives more contribution to large states.</t>
-  </si>
-  <si>
-    <t>Summarizes the importance of the variables defining societal features to different fishers. The algorithm wmax gives more contribution to large states.</t>
-  </si>
-  <si>
-    <t>The capacity to pursue different avenues (in fishing, marketing, technology, etc.) and to adapt to changing circumstances. The algorithm wmax gives more contribution to large states.</t>
-  </si>
-  <si>
-    <t>Summarizes the importance of the variables defining economic features to different fishers. The algorithm wmin gives more contribution to small states.</t>
-  </si>
-  <si>
     <t>Case C1 based on question Q 23</t>
   </si>
   <si>
@@ -362,9 +350,6 @@
     <t>Case C2. Weight based on questions Q21 a, b and c. Algorithm is wmin</t>
   </si>
   <si>
-    <t>Summarizes the non-monetary outcomes associated to the fishing experience. It depends on the possibility to go out fishing and to obtain satisfying catches, while staying safe. The wmin algorithm implies that all the conditions are necessary to obtain a large value.</t>
-  </si>
-  <si>
     <t>Case C5</t>
   </si>
   <si>
@@ -374,28 +359,16 @@
     <t>Availability of terrestrial infrastructures such as roads, ports and bridges</t>
   </si>
   <si>
-    <t>Fishers strategy is coded as adapt, react or cope (Green et al., 2021). Adapt is proactive planning, it implies large changes in fishing strategy (i.e.: changing fishing target and/or gear). React is unplanned response, or small modification to fishing practice practice (fishing in a diferent location or in different time of the day). Cope is passively accepting consequences, it implies no modifications at all to the fishing strategy</t>
-  </si>
-  <si>
     <t>Measures implemented in the case when the strategy is React. The different solutions work differently and have different cost: travel further implies fishers change fishing location to seek a sheltered place or to find deeper waters; short sets mean that the fisher perform shorter sessions than average (i.e.: reduced soak time for gillnets); other technical includes strategies that are mentioned sporadically (i.e.: use of ice machines)</t>
   </si>
   <si>
-    <t>The ability to catch fish depending on gear-fish interactions. For example, a gillnet clogged in algae is more visible and less efficient (less catchability).</t>
-  </si>
-  <si>
     <t>The real or perceived quality of catches in terms of aspect/health status. Does NOT refer to species composition or distribution. There are some "technical solutions" that balance for negative effects of MEW</t>
   </si>
   <si>
-    <t>Any variation to ordinary working condition that can increase the potential physical damage for operators (i.e.: slipping; a violent storm is life threatening). There are some "technical solutions" that balance for negative effects of MEW</t>
-  </si>
-  <si>
     <t>Damage to the fishing gear ranging from minor to completely losing the fishing gear or part of it because it was lost or irreparably damaged. There are some "technical solutions" that balance for negative effects of MEW</t>
   </si>
   <si>
     <t>The probability to go out fishing</t>
-  </si>
-  <si>
-    <t>The most probable target species associated to each fishing gear. The levels describes the 5 most common species that are relevant across the fishing styles, one aggregation for whitefish (including Common whitefish and vendace), and one category to group any other species. The category not_specified is also assigned to inland and not relevant</t>
   </si>
   <si>
     <t>Psychological aspect, elements such as anxiety and sense of fatigue (Chatterjee and and Bolar, 2019). The stressful events considered are having damages to the gear, being injuried, being the catch in poor condition</t>
@@ -438,9 +411,6 @@
 </t>
   </si>
   <si>
-    <t>The impact of a lost day is not determined by the loss itself, but by its recoverability. When value is tied to outcomes, time can be lost and later absorbed. When value is tied to time itself, loss becomes irreversible.</t>
-  </si>
-  <si>
     <t>monetary_loss</t>
   </si>
   <si>
@@ -499,6 +469,36 @@
   </si>
   <si>
     <t>Most probable gear used by each fisher. Terminology is mostly inspired by codes used in the European Data Collection Framework (https://dcf.ec.europa.eu/data-calls/definitions-and-terminology/g/gear_en). Otm is pelagic (midwater) otter-trawl; gns_spf is gillnets targeting small pelagic fish; gns_fws is gillnets targeting freshwater species; fpn_ana is traps (or pots) targeting anadromous species; lhp is Handlines and pole-lines (hand-operated); icefishing is fishing with lines by carving holes on iced surfaces of coastal areas and lakes; inland is a general description for any fishing activity poerformed in lakes and rivers</t>
+  </si>
+  <si>
+    <t>The ability to catch fish depending on gear-fish interactions. For example, a gillnet clogged in algae is more visible and less efficient (less catchability)</t>
+  </si>
+  <si>
+    <t>The impact of a lost day is not determined by the loss itself, but by its recoverability. When value is tied to outcomes, time can be lost and later absorbed. When value is tied to time itself, loss becomes irreversible</t>
+  </si>
+  <si>
+    <t>Summarizes the non-monetary outcomes associated to the fishing experience. It depends on the possibility to go out fishing and to obtain satisfying catches, while staying safe. The wmin algorithm implies that all the conditions are necessary to obtain a large value</t>
+  </si>
+  <si>
+    <t>The capacity to pursue different avenues (in fishing, marketing, technology, etc.) and to adapt to changing circumstances. The algorithm wmax gives more contribution to large states</t>
+  </si>
+  <si>
+    <t>Summarizes the importance of the variables defining economic features to different fishers. The algorithm wmin gives more contribution to small states</t>
+  </si>
+  <si>
+    <t>Summarizes the importance of the variables defining societal features to different fishers. The algorithm wmax gives more contribution to large states</t>
+  </si>
+  <si>
+    <t>Summarizes the importance of the variables defining individual features to different fishers. The algorithm wmax gives more contribution to large states</t>
+  </si>
+  <si>
+    <t>Any variation to ordinary working conditions that can increase the potential physical damage for operators (i.e.: slipping; a violent storm is life threatening). There are some "technical solutions" that balance for negative effects of MEW</t>
+  </si>
+  <si>
+    <t>The most probable target species associated to each fishing gear. The levels describe the 5 most common species that are relevant across the fishing styles, one aggregation for whitefish (including Common whitefish and vendace), and one category to group any other species. The category not_specified is also assigned to inland and not relevant</t>
+  </si>
+  <si>
+    <t>Fishers strategy is coded as adapt, react or cope (Green et al., 2021). Adapt is proactive planning, it implies large changes in fishing strategy (i.e.: changing fishing target and/or gear). React is unplanned response, or small modification to fishing practice (fishing in a diferent location or in different time of the day). Cope is passively accepting consequences, it implies no modifications at all to the fishing strategy</t>
   </si>
 </sst>
 </file>
@@ -924,7 +924,7 @@
     </row>
     <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -950,7 +950,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>73</v>
       </c>
@@ -966,7 +966,7 @@
     </row>
     <row r="5" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -975,10 +975,10 @@
         <v>74</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -995,7 +995,7 @@
         <v>52</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>81</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="7" spans="1:7" ht="117" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
@@ -1015,10 +1015,10 @@
         <v>69</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1035,10 +1035,10 @@
         <v>53</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="144" x14ac:dyDescent="0.3">
@@ -1055,10 +1055,10 @@
         <v>63</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -1075,10 +1075,10 @@
         <v>54</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1095,10 +1095,10 @@
         <v>55</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -1115,10 +1115,10 @@
         <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="72" x14ac:dyDescent="0.3">
@@ -1135,10 +1135,10 @@
         <v>68</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1155,15 +1155,15 @@
         <v>67</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
@@ -1175,10 +1175,10 @@
         <v>57</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1195,10 +1195,10 @@
         <v>58</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1215,10 +1215,10 @@
         <v>78</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1235,10 +1235,10 @@
         <v>64</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1255,15 +1255,15 @@
         <v>65</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -1275,15 +1275,15 @@
         <v>70</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C21" s="1">
         <v>3</v>
@@ -1292,13 +1292,13 @@
         <v>49</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1315,15 +1315,15 @@
         <v>66</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C23" s="1">
         <v>3</v>
@@ -1332,10 +1332,10 @@
         <v>48</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -1355,7 +1355,7 @@
         <v>34</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -1375,7 +1375,7 @@
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -1392,10 +1392,10 @@
         <v>35</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>84</v>
+        <v>149</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H26" s="1"/>
     </row>
@@ -1410,13 +1410,13 @@
         <v>48</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -1436,7 +1436,7 @@
         <v>32</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -1453,15 +1453,15 @@
         <v>79</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C30" s="1">
         <v>4</v>
@@ -1470,13 +1470,13 @@
         <v>48</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -1496,7 +1496,7 @@
         <v>59</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -1513,10 +1513,10 @@
         <v>60</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1536,7 +1536,7 @@
         <v>61</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.3">
@@ -1553,10 +1553,10 @@
         <v>36</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1573,10 +1573,10 @@
         <v>79</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1596,12 +1596,12 @@
         <v>37</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C37" s="1">
         <v>2</v>
@@ -1616,7 +1616,7 @@
         <v>39</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1636,7 +1636,7 @@
         <v>38</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1653,10 +1653,10 @@
         <v>79</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1673,10 +1673,10 @@
         <v>43</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1693,10 +1693,10 @@
         <v>42</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1713,10 +1713,10 @@
         <v>41</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
